--- a/data/trans_orig/IP04D$aparatos-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$aparatos-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89290</t>
+          <t>89774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>108210</t>
+          <t>108026</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92201</t>
+          <t>91741</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111740</t>
+          <t>111942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>187935</t>
+          <t>187796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214944</t>
+          <t>214221</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,09%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>30362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49098</t>
+          <t>48614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42944</t>
+          <t>42742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62483</t>
+          <t>62943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78128</t>
+          <t>78851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105137</t>
+          <t>105276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,92%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119872</t>
+          <t>117835</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>142569</t>
+          <t>140237</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137606</t>
+          <t>135917</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159806</t>
+          <t>159928</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>262539</t>
+          <t>262118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295535</t>
+          <t>292721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62450</t>
+          <t>64782</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85147</t>
+          <t>87184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64029</t>
+          <t>63907</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86229</t>
+          <t>87918</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133319</t>
+          <t>136133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166315</t>
+          <t>166736</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,88%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>100696</t>
+          <t>100750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118884</t>
+          <t>118600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100357</t>
+          <t>99806</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119642</t>
+          <t>119267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207012</t>
+          <t>206765</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233327</t>
+          <t>232740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36492</t>
+          <t>36776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54680</t>
+          <t>54626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>46043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>64953</t>
+          <t>65504</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87359</t>
+          <t>87946</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113674</t>
+          <t>113921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>103144</t>
+          <t>103724</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128869</t>
+          <t>128187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92754</t>
+          <t>92546</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117276</t>
+          <t>117317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>203189</t>
+          <t>204545</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>238302</t>
+          <t>239731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80641</t>
+          <t>81323</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>106366</t>
+          <t>105786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91120</t>
+          <t>91079</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115642</t>
+          <t>115850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>179604</t>
+          <t>178175</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>214717</t>
+          <t>213361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>435016</t>
+          <t>433746</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>476483</t>
+          <t>477138</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>442269</t>
+          <t>444078</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>486898</t>
+          <t>487362</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>890540</t>
+          <t>890450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>951405</t>
+          <t>953410</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,28%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>231809</t>
+          <t>231154</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>273276</t>
+          <t>274546</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>265327</t>
+          <t>264863</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>309956</t>
+          <t>308147</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>509112</t>
+          <t>507107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569977</t>
+          <t>570067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59303</t>
+          <t>60421</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78854</t>
+          <t>79506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72233</t>
+          <t>72016</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91977</t>
+          <t>92902</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138120</t>
+          <t>136801</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164825</t>
+          <t>165851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>59,03%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54018</t>
+          <t>53366</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73569</t>
+          <t>72451</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56099</t>
+          <t>55174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>75843</t>
+          <t>76060</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116123</t>
+          <t>115097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>142828</t>
+          <t>144147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100578</t>
+          <t>101247</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>122525</t>
+          <t>122949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108368</t>
+          <t>108878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133026</t>
+          <t>133582</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>216803</t>
+          <t>216055</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248799</t>
+          <t>248918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,93%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83454</t>
+          <t>83030</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105401</t>
+          <t>104732</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90662</t>
+          <t>90106</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115320</t>
+          <t>114810</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180868</t>
+          <t>180749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212864</t>
+          <t>213612</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61334</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80606</t>
+          <t>80010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59571</t>
+          <t>61463</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80180</t>
+          <t>80706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126484</t>
+          <t>127542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156221</t>
+          <t>157436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,91%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75391</t>
+          <t>75987</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94663</t>
+          <t>94774</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85734</t>
+          <t>85208</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106343</t>
+          <t>104451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165690</t>
+          <t>164475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>195427</t>
+          <t>194369</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,38%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>99560</t>
+          <t>98208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123347</t>
+          <t>122670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106020</t>
+          <t>104537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126535</t>
+          <t>127609</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>208484</t>
+          <t>211253</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242537</t>
+          <t>242922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81985</t>
+          <t>82662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105772</t>
+          <t>107124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75798</t>
+          <t>74724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96313</t>
+          <t>97796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165128</t>
+          <t>164743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>199181</t>
+          <t>196412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>341465</t>
+          <t>340584</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>382945</t>
+          <t>383439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>367598</t>
+          <t>366690</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>413510</t>
+          <t>411755</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>720906</t>
+          <t>722137</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>781491</t>
+          <t>784270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,46%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>317236</t>
+          <t>316742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>358716</t>
+          <t>359597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>326501</t>
+          <t>328256</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>372413</t>
+          <t>373321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>658701</t>
+          <t>655922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>719286</t>
+          <t>718055</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69386</t>
+          <t>67901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84978</t>
+          <t>85110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62166</t>
+          <t>62745</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97056</t>
+          <t>97738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>134782</t>
+          <t>135221</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175687</t>
+          <t>175468</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32302</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>49379</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43356</t>
+          <t>42674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78246</t>
+          <t>77667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82006</t>
+          <t>82225</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122911</t>
+          <t>122472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100890</t>
+          <t>102557</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128341</t>
+          <t>127400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148527</t>
+          <t>150442</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177925</t>
+          <t>176855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260891</t>
+          <t>260916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>298872</t>
+          <t>297807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,1%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61172</t>
+          <t>62113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88623</t>
+          <t>86956</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>77473</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105801</t>
+          <t>103886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144969</t>
+          <t>146034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182950</t>
+          <t>182925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117174</t>
+          <t>116327</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154029</t>
+          <t>154041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93008</t>
+          <t>91788</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>120520</t>
+          <t>119638</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>217267</t>
+          <t>216902</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>271575</t>
+          <t>271994</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36372</t>
+          <t>36360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73227</t>
+          <t>74074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>64766</t>
+          <t>65648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92278</t>
+          <t>93498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>104112</t>
+          <t>103693</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158420</t>
+          <t>158785</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,27%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78784</t>
+          <t>79264</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101054</t>
+          <t>101749</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>79465</t>
+          <t>80098</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104086</t>
+          <t>103750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164416</t>
+          <t>164436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>197583</t>
+          <t>195747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66908</t>
+          <t>66213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>89178</t>
+          <t>88698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76209</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100830</t>
+          <t>100197</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150674</t>
+          <t>152510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183841</t>
+          <t>183821</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,78%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>390190</t>
+          <t>391941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>449372</t>
+          <t>454634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>413919</t>
+          <t>411370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>476641</t>
+          <t>473302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>820184</t>
+          <t>822563</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>907555</t>
+          <t>903394</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>215784</t>
+          <t>210522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>274966</t>
+          <t>273215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>283681</t>
+          <t>287020</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>346403</t>
+          <t>348952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>517922</t>
+          <t>522083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>605293</t>
+          <t>602914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP04D$aparatos-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP04D$aparatos-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>101701</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91459</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>112254</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>59,13%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>72,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>99177</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>89774</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>108026</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>89537</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>108114</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>71,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>64,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,06%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>101701</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>91741</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>111942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,75%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>187796</t>
+          <t>186151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214221</t>
+          <t>212183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,4%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52983</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>42430</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63225</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>40,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>39211</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>30362</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48614</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>30274</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48851</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>28,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>21,94%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>52983</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>42742</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>62943</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78851</t>
+          <t>80889</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105276</t>
+          <t>106921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138388</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>148690</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>135628</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>159723</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,43%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>130163</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>117835</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>140237</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>118658</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>140406</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>63,49%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>57,47%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>68,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>148690</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>135917</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>159928</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>66,43%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>262118</t>
+          <t>260877</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>292721</t>
+          <t>293427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75145</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64112</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>88207</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,57%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>39,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>74856</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>64782</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>87184</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>64613</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>86361</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>36,51%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>42,53%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>75145</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>63907</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>87918</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136133</t>
+          <t>135427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166736</t>
+          <t>167977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205019</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>110281</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100206</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>119526</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>72,3%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>172</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>110055</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>100750</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>118600</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>100533</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>119260</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>70,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>64,84%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>110281</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>99806</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>119267</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>66,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206765</t>
+          <t>206904</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>232740</t>
+          <t>234542</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>55029</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45784</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>65104</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>33,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>45321</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36776</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>54626</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>36116</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>54843</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>29,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>35,16%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>55029</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>46043</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>65504</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>33,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87946</t>
+          <t>86144</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113921</t>
+          <t>113782</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165310</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>104631</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>92011</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>116283</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50,21%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>44,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>55,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>116554</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>103724</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>128187</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>104351</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>128826</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>55,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>49,51%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>61,18%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>104631</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>92546</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>117317</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>50,21%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>204545</t>
+          <t>205748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239731</t>
+          <t>239774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,38%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>103765</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>92113</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116385</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>49,79%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>44,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>55,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>92956</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>81323</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>105786</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>80684</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>105159</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>44,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>38,82%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>50,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>103765</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>91079</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>115850</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>49,79%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>178175</t>
+          <t>178132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>213361</t>
+          <t>212158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>50,77%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208396</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209510</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>465303</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>444098</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>487265</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>61,86%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>59,04%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>64,78%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>660</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>455948</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>433746</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>477138</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>436076</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>477724</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>61,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>67,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>465303</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>444078</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>487362</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>61,86%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>890450</t>
+          <t>890344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>953410</t>
+          <t>952094</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,19%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>286922</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>264960</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>308127</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,14%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>35,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>40,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>361</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>252344</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>231154</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>274546</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>230568</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>272216</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,64%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>38,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>286922</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>264863</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>308147</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,14%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>507107</t>
+          <t>508423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570067</t>
+          <t>570173</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>752225</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1021</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>708292</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>752225</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>82376</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72150</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>92652</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>55,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>48,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>69201</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>60421</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>79506</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>58833</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>79096</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>52,08%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>45,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>59,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>82376</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>72016</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>92902</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>55,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>136801</t>
+          <t>138331</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165851</t>
+          <t>167112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>65700</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>55424</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>75926</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,37%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>63671</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53366</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>72451</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>53776</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>74039</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>47,92%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>40,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>54,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>65700</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>55174</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>76060</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,37%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115097</t>
+          <t>113836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144147</t>
+          <t>142617</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>50,76%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>132872</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121600</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>108519</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>132122</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>54,36%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>48,51%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>59,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>111675</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>101247</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>122949</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>99544</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>121408</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>54,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>49,15%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>59,69%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>121600</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>108878</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>133582</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>54,36%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>216055</t>
+          <t>215812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248918</t>
+          <t>248271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>102088</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>91566</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>115169</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>45,64%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>51,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>94304</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>83030</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>104732</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>84571</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>106435</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>45,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>50,85%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>102088</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>90106</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>114810</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>45,64%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>180749</t>
+          <t>181396</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>213612</t>
+          <t>213855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,77%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223688</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223688</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70594</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59631</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>80916</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>70791</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>61223</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>80010</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>61400</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>80679</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>45,38%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,25%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,29%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>70594</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>61463</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>80706</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>127542</t>
+          <t>127334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157436</t>
+          <t>156181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>95320</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>84998</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>106283</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,45%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>85206</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>75987</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>94774</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>75318</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>94597</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>54,62%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>48,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>60,75%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>95320</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>85208</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104451</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>57,45%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164475</t>
+          <t>165730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>194369</t>
+          <t>194577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,44%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165914</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165914</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>115932</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>105318</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>127277</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>57,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>62,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>110672</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>98208</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>122670</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>98540</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>122931</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>53,9%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>47,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>115932</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>104537</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>127609</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>57,3%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>211253</t>
+          <t>210301</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242922</t>
+          <t>244179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>86401</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75056</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>97015</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>37,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>47,95%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>94660</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>82662</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>107124</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>82401</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>106792</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>46,1%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>86401</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>74724</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>97796</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>42,7%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>164743</t>
+          <t>163486</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196412</t>
+          <t>197364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202333</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205332</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202333</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>390501</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>367827</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>410849</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>49,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>538</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>362339</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>340584</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>383439</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>340992</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>383063</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>51,75%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>54,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>390501</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>366690</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>411755</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>722137</t>
+          <t>722197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>784270</t>
+          <t>783510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>349510</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>329162</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>372184</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>517</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>337842</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>316742</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>359597</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>317118</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>359189</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>48,25%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>45,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>349510</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>328256</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>373321</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>655922</t>
+          <t>656682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>718055</t>
+          <t>717995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1058</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>740011</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>700181</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>740011</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>78732</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>60329</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>89356</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47,92%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>77427</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>67901</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>85110</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>66,02%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>57,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>72,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>83233</t>
+          <t>80974</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62745</t>
+          <t>72014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97738</t>
+          <t>89326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>160660</t>
+          <t>159705</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135221</t>
+          <t>140200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175468</t>
+          <t>173540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>47174</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36550</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>65577</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>52,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>39853</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>32170</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>49379</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>42,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57179</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42674</t>
+          <t>31745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77667</t>
+          <t>49057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>97033</t>
+          <t>87272</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>82225</t>
+          <t>73437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>122472</t>
+          <t>106777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>156816</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>143870</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>169415</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>66,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>60,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>71,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>179</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>116573</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>102557</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>127400</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>61,51%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>54,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>67,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>164075</t>
+          <t>117013</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>150442</t>
+          <t>105138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176855</t>
+          <t>127869</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5034,32 +5034,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>280648</t>
+          <t>273829</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260916</t>
+          <t>255356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>297807</t>
+          <t>291093</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>69,32%</t>
         </is>
       </c>
     </row>
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79774</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>67175</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92720</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>33,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,39%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>39,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>72940</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>62113</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>86956</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>38,49%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>90253</t>
+          <t>66324</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77473</t>
+          <t>55468</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103886</t>
+          <t>78199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>163193</t>
+          <t>146098</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>146034</t>
+          <t>128834</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182925</t>
+          <t>164571</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236590</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>189513</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>254328</t>
+          <t>183337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>443841</t>
+          <t>419927</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>98373</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86319</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>110967</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58,44%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>51,28%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>65,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>132117</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>116327</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>154041</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>69,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>61,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>106393</t>
+          <t>104487</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91788</t>
+          <t>94145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119638</t>
+          <t>114139</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>238509</t>
+          <t>202861</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>216902</t>
+          <t>185113</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>271994</t>
+          <t>218124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>67,03%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69968</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57374</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>82022</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>41,56%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>48,72%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>58284</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36360</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74074</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>30,61%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>38,9%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78893</t>
+          <t>52563</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65648</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93498</t>
+          <t>62905</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>137178</t>
+          <t>122530</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103693</t>
+          <t>107267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158785</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>86224</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>74315</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>97369</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>44,13%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>57,81%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>89790</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>79264</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>101749</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>53,46%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>47,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91988</t>
+          <t>89747</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80098</t>
+          <t>79449</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103750</t>
+          <t>100529</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>181778</t>
+          <t>175972</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>164436</t>
+          <t>159352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195747</t>
+          <t>190245</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>78172</t>
+          <t>82195</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66213</t>
+          <t>71050</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88698</t>
+          <t>94104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>88307</t>
+          <t>77398</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76545</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100197</t>
+          <t>87696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>166479</t>
+          <t>159592</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152510</t>
+          <t>145319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>183821</t>
+          <t>176212</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,51%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>348257</t>
+          <t>335564</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>420145</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>393508</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>445390</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>60,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>63,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>589</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>415906</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>391941</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>454634</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>62,53%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>445689</t>
+          <t>392221</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>411370</t>
+          <t>372390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>473302</t>
+          <t>411409</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>861595</t>
+          <t>812366</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>822563</t>
+          <t>779070</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>903394</t>
+          <t>843161</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,5%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>279111</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>253866</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>305748</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>43,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>353</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>249250</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>210522</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>273215</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>37,47%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,65%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>314633</t>
+          <t>236382</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>287020</t>
+          <t>217194</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>348952</t>
+          <t>256213</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>563882</t>
+          <t>515493</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>522083</t>
+          <t>484698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>602914</t>
+          <t>548789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699256</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665156</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760322</t>
+          <t>628603</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425477</t>
+          <t>1327859</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
